--- a/exports/trend_1d/ICICIGI_full_report.xlsx
+++ b/exports/trend_1d/ICICIGI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.09</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43178</v>
+        <v>43179</v>
       </c>
       <c r="H2" t="n">
-        <v>770.5</v>
+        <v>757.75</v>
       </c>
       <c r="I2" t="n">
         <v>763.5362501942684</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K2" t="n">
-        <v>10.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>4.67</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43299</v>
+        <v>43300</v>
       </c>
       <c r="H3" t="n">
-        <v>750.7</v>
+        <v>763.15</v>
       </c>
       <c r="I3" t="n">
         <v>753.8598555538807</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K3" t="n">
-        <v>0.93</v>
+        <v>-0.71</v>
       </c>
       <c r="L3" t="n">
         <v>6.2</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.24</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H4" t="n">
-        <v>844.95</v>
+        <v>808.35</v>
       </c>
       <c r="I4" t="n">
         <v>811.7163592762143</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" t="n">
-        <v>10.72</v>
+        <v>5.92</v>
       </c>
       <c r="L4" t="n">
         <v>4.93</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>18.46</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43437</v>
+        <v>43438</v>
       </c>
       <c r="H5" t="n">
-        <v>858.3</v>
+        <v>886.6</v>
       </c>
       <c r="I5" t="n">
         <v>866.5367976858306</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.18</v>
+        <v>-9.68</v>
       </c>
       <c r="L5" t="n">
-        <v>8.619999999999999</v>
+        <v>11.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.43</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.15</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H6" t="n">
-        <v>1105.6</v>
+        <v>1068.95</v>
       </c>
       <c r="I6" t="n">
         <v>1071.998196434922</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K6" t="n">
-        <v>24.7</v>
+        <v>20.57</v>
       </c>
       <c r="L6" t="n">
         <v>8.98</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.46</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43672</v>
+        <v>43675</v>
       </c>
       <c r="H7" t="n">
-        <v>1140.8</v>
+        <v>1174</v>
       </c>
       <c r="I7" t="n">
         <v>1144.70625607565</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.72</v>
+        <v>-9.83</v>
       </c>
       <c r="L7" t="n">
-        <v>7.58</v>
+        <v>10.28</v>
       </c>
       <c r="M7" t="n">
         <v>1.27</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>11.63</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H8" t="n">
-        <v>1178.4</v>
+        <v>1129.2</v>
       </c>
       <c r="I8" t="n">
         <v>1131.496240967877</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K8" t="n">
-        <v>0.37</v>
+        <v>-3.82</v>
       </c>
       <c r="L8" t="n">
         <v>5.75</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1</v>
+        <v>3.26</v>
       </c>
       <c r="N8" t="n">
         <v>5.39</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.85</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43752</v>
+        <v>43753</v>
       </c>
       <c r="H9" t="n">
-        <v>1241.25</v>
+        <v>1265.9</v>
       </c>
       <c r="I9" t="n">
         <v>1243.070996495788</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.92</v>
+        <v>-12.11</v>
       </c>
       <c r="L9" t="n">
         <v>12.47</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43851</v>
+        <v>43852</v>
       </c>
       <c r="H10" t="n">
-        <v>1329.95</v>
+        <v>1313.6</v>
       </c>
       <c r="I10" t="n">
         <v>1326.071213787867</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K10" t="n">
-        <v>5.06</v>
+        <v>3.77</v>
       </c>
       <c r="L10" t="n">
         <v>7.17</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H11" t="n">
-        <v>1231.25</v>
+        <v>1290.6</v>
       </c>
       <c r="I11" t="n">
         <v>1240.164048949269</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K11" t="n">
-        <v>6.27</v>
+        <v>1.75</v>
       </c>
       <c r="L11" t="n">
         <v>6.43</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>20.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44067</v>
+        <v>44068</v>
       </c>
       <c r="H12" t="n">
-        <v>1275.15</v>
+        <v>1265.35</v>
       </c>
       <c r="I12" t="n">
         <v>1270.691495943039</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2</v>
+        <v>-1.96</v>
       </c>
       <c r="L12" t="n">
         <v>12.83</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>10.81</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H13" t="n">
-        <v>1295.9</v>
+        <v>1329.2</v>
       </c>
       <c r="I13" t="n">
         <v>1326.739920774388</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.41</v>
+        <v>-5.05</v>
       </c>
       <c r="L13" t="n">
-        <v>5.51</v>
+        <v>5.79</v>
       </c>
       <c r="M13" t="n">
         <v>1.55</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44216</v>
+        <v>44217</v>
       </c>
       <c r="H14" t="n">
-        <v>1494.9</v>
+        <v>1462.85</v>
       </c>
       <c r="I14" t="n">
         <v>1474.872391125018</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K14" t="n">
-        <v>12.47</v>
+        <v>10.05</v>
       </c>
       <c r="L14" t="n">
         <v>3.88</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11.55</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="H15" t="n">
-        <v>1473</v>
+        <v>1512.8</v>
       </c>
       <c r="I15" t="n">
         <v>1509.212580715731</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.41</v>
       </c>
       <c r="L15" t="n">
-        <v>3.84</v>
+        <v>4.93</v>
       </c>
       <c r="M15" t="n">
         <v>2.68</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>12.48</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H16" t="n">
-        <v>1419.6</v>
+        <v>1351.05</v>
       </c>
       <c r="I16" t="n">
         <v>1377.915213725041</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.16</v>
+        <v>-10.69</v>
       </c>
       <c r="L16" t="n">
-        <v>8.94</v>
+        <v>12.09</v>
       </c>
       <c r="M16" t="n">
         <v>0.88</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>4.83</v>
       </c>
       <c r="O16" t="n">
         <v>2.7</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.68</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44334</v>
+        <v>44335</v>
       </c>
       <c r="H17" t="n">
-        <v>1487.05</v>
+        <v>1504.95</v>
       </c>
       <c r="I17" t="n">
         <v>1500.146911165121</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.07</v>
+        <v>-11.39</v>
       </c>
       <c r="L17" t="n">
         <v>12.36</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44400</v>
+        <v>44403</v>
       </c>
       <c r="H18" t="n">
-        <v>1484.8</v>
+        <v>1455.95</v>
       </c>
       <c r="I18" t="n">
         <v>1476.043938259246</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.34</v>
+        <v>-3.26</v>
       </c>
       <c r="L18" t="n">
         <v>4.98</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>10.39</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44434</v>
+        <v>44435</v>
       </c>
       <c r="H19" t="n">
-        <v>1471.15</v>
+        <v>1557.7</v>
       </c>
       <c r="I19" t="n">
         <v>1532.089837996394</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.04</v>
+        <v>-6.99</v>
       </c>
       <c r="L19" t="n">
-        <v>3.98</v>
+        <v>7.68</v>
       </c>
       <c r="M19" t="n">
         <v>0.82</v>
       </c>
       <c r="N19" t="n">
-        <v>2.31</v>
+        <v>5.88</v>
       </c>
       <c r="O19" t="n">
         <v>-1.94</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H20" t="n">
-        <v>1529.2</v>
+        <v>1504.4</v>
       </c>
       <c r="I20" t="n">
         <v>1516.356572747967</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.83</v>
+        <v>-3.42</v>
       </c>
       <c r="L20" t="n">
         <v>5.13</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.46</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H21" t="n">
-        <v>1423.6</v>
+        <v>1449.55</v>
       </c>
       <c r="I21" t="n">
         <v>1444.299322524789</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K21" t="n">
-        <v>5.37</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>2.91</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.61</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H22" t="n">
-        <v>1381.65</v>
+        <v>1331</v>
       </c>
       <c r="I22" t="n">
         <v>1354.615526587177</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.68</v>
+        <v>-8.18</v>
       </c>
       <c r="L22" t="n">
         <v>9.07</v>
@@ -1695,7 +1958,7 @@
         <v>2.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2.57</v>
+        <v>3.67</v>
       </c>
       <c r="O22" t="n">
         <v>1.82</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.57</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44649</v>
+        <v>44650</v>
       </c>
       <c r="H23" t="n">
-        <v>1275.85</v>
+        <v>1329.9</v>
       </c>
       <c r="I23" t="n">
         <v>1318.427934174617</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K23" t="n">
-        <v>4.14</v>
+        <v>0.08</v>
       </c>
       <c r="L23" t="n">
         <v>6.37</v>
@@ -1752,7 +2027,7 @@
         <v>2.11</v>
       </c>
       <c r="N23" t="n">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="O23" t="n">
         <v>-3.67</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>10.05</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44679</v>
+        <v>44680</v>
       </c>
       <c r="H24" t="n">
-        <v>1337.5</v>
+        <v>1280.2</v>
       </c>
       <c r="I24" t="n">
         <v>1287.796268316678</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.57</v>
+        <v>-3.74</v>
       </c>
       <c r="L24" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="M24" t="n">
         <v>4</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.03</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H25" t="n">
-        <v>1187.05</v>
+        <v>1232.25</v>
       </c>
       <c r="I25" t="n">
         <v>1212.146262466666</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K25" t="n">
-        <v>7.28</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>4.9</v>
@@ -1866,7 +2165,7 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>3.81</v>
       </c>
       <c r="O25" t="n">
         <v>-4.28</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>10.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44767</v>
+        <v>44768</v>
       </c>
       <c r="H26" t="n">
-        <v>1189.2</v>
+        <v>1157</v>
       </c>
       <c r="I26" t="n">
         <v>1170.20432037312</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.49</v>
+        <v>-6.11</v>
       </c>
       <c r="L26" t="n">
-        <v>4.16</v>
+        <v>6.35</v>
       </c>
       <c r="M26" t="n">
         <v>0.4</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.36</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44785</v>
+        <v>44789</v>
       </c>
       <c r="H27" t="n">
-        <v>1237.85</v>
+        <v>1296</v>
       </c>
       <c r="I27" t="n">
         <v>1276.890544862876</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.99</v>
+        <v>-12.01</v>
       </c>
       <c r="L27" t="n">
-        <v>8.15</v>
+        <v>12.53</v>
       </c>
       <c r="M27" t="n">
         <v>0.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2.71</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
         <v>-2.71</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44809</v>
+        <v>44810</v>
       </c>
       <c r="H28" t="n">
-        <v>1261.85</v>
+        <v>1218.95</v>
       </c>
       <c r="I28" t="n">
         <v>1229.562667430215</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.64</v>
+        <v>-5.95</v>
       </c>
       <c r="L28" t="n">
-        <v>5.86</v>
+        <v>6.33</v>
       </c>
       <c r="M28" t="n">
         <v>1.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="O28" t="n">
         <v>4.7</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.56</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44894</v>
+        <v>44895</v>
       </c>
       <c r="H29" t="n">
-        <v>1175.7</v>
+        <v>1211.15</v>
       </c>
       <c r="I29" t="n">
         <v>1187.753896508864</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>0.64</v>
       </c>
       <c r="L29" t="n">
         <v>5.24</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>7.03</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44944</v>
+        <v>44945</v>
       </c>
       <c r="H30" t="n">
-        <v>1200.15</v>
+        <v>1169.6</v>
       </c>
       <c r="I30" t="n">
         <v>1190.57561601434</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.91</v>
+        <v>-3.43</v>
       </c>
       <c r="L30" t="n">
-        <v>3.03</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
         <v>1.22</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45033</v>
+        <v>45034</v>
       </c>
       <c r="H31" t="n">
-        <v>1104.1</v>
+        <v>1130.75</v>
       </c>
       <c r="I31" t="n">
         <v>1125.997586990383</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" t="n">
-        <v>5.6</v>
+        <v>3.32</v>
       </c>
       <c r="L31" t="n">
         <v>2.4</v>
@@ -2208,7 +2579,7 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>1.51</v>
+        <v>2.41</v>
       </c>
       <c r="O31" t="n">
         <v>-2.55</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H32" t="n">
-        <v>1303.6</v>
+        <v>1274.25</v>
       </c>
       <c r="I32" t="n">
         <v>1299.169547980109</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K32" t="n">
-        <v>15.29</v>
+        <v>12.69</v>
       </c>
       <c r="L32" t="n">
         <v>6.7</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>6.88</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45217</v>
+        <v>45218</v>
       </c>
       <c r="H33" t="n">
-        <v>1358.55</v>
+        <v>1371.7</v>
       </c>
       <c r="I33" t="n">
         <v>1361.875409658669</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.62</v>
+        <v>-7.65</v>
       </c>
       <c r="L33" t="n">
-        <v>7.39</v>
+        <v>10.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="N33" t="n">
         <v>2.77</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.23</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45303</v>
+        <v>45306</v>
       </c>
       <c r="H34" t="n">
-        <v>1394.1</v>
+        <v>1372.8</v>
       </c>
       <c r="I34" t="n">
         <v>1377.188386128685</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K34" t="n">
-        <v>1.63</v>
+        <v>0.08</v>
       </c>
       <c r="L34" t="n">
         <v>2.88</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.44</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H35" t="n">
-        <v>1374.2</v>
+        <v>1454.45</v>
       </c>
       <c r="I35" t="n">
         <v>1450.140013094237</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.1</v>
+        <v>-5.95</v>
       </c>
       <c r="L35" t="n">
-        <v>3.23</v>
+        <v>7.52</v>
       </c>
       <c r="M35" t="n">
-        <v>1.21</v>
+        <v>2.61</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1</v>
+        <v>5.84</v>
       </c>
       <c r="O35" t="n">
         <v>-1.53</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.95</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H36" t="n">
-        <v>1596.85</v>
+        <v>1586.15</v>
       </c>
       <c r="I36" t="n">
         <v>1592.970960471438</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K36" t="n">
-        <v>9.789999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>3.05</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.67</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H37" t="n">
-        <v>1662.7</v>
+        <v>1730.9</v>
       </c>
       <c r="I37" t="n">
         <v>1688.267787088244</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.83</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>6.54</v>
+        <v>11.4</v>
       </c>
       <c r="M37" t="n">
         <v>3.12</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.48</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H38" t="n">
-        <v>2122.45</v>
+        <v>2109.25</v>
       </c>
       <c r="I38" t="n">
         <v>2113.771182886613</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K38" t="n">
-        <v>22.62</v>
+        <v>21.86</v>
       </c>
       <c r="L38" t="n">
         <v>5.19</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>8.51</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45555</v>
+        <v>45558</v>
       </c>
       <c r="H39" t="n">
-        <v>2234.05</v>
+        <v>2275.2</v>
       </c>
       <c r="I39" t="n">
         <v>2247.9104223035</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.92</v>
+        <v>-7.87</v>
       </c>
       <c r="L39" t="n">
-        <v>6.89</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>0.91</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>7.63</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H40" t="n">
-        <v>2126.6</v>
+        <v>2100.8</v>
       </c>
       <c r="I40" t="n">
         <v>2101.668271926674</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.53</v>
+        <v>-7.67</v>
       </c>
       <c r="L40" t="n">
-        <v>6.96</v>
+        <v>8.56</v>
       </c>
       <c r="M40" t="n">
         <v>0.65</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.6</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="H41" t="n">
-        <v>1961.35</v>
+        <v>1983.35</v>
       </c>
       <c r="I41" t="n">
         <v>1976.501935546108</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K41" t="n">
-        <v>6.64</v>
+        <v>5.59</v>
       </c>
       <c r="L41" t="n">
         <v>3.09</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.76</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="H42" t="n">
-        <v>1861.15</v>
+        <v>1832.45</v>
       </c>
       <c r="I42" t="n">
         <v>1836.571583845151</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.16</v>
+        <v>-7.61</v>
       </c>
       <c r="L42" t="n">
-        <v>7.5</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0.73</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.73</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H43" t="n">
-        <v>1907.9</v>
+        <v>1948.75</v>
       </c>
       <c r="I43" t="n">
         <v>1931.468378246404</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.12</v>
+        <v>-6.35</v>
       </c>
       <c r="L43" t="n">
-        <v>5.32</v>
+        <v>7.29</v>
       </c>
       <c r="M43" t="n">
         <v>0.52</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.68</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="H44" t="n">
-        <v>1795.1</v>
+        <v>1764.8</v>
       </c>
       <c r="I44" t="n">
         <v>1771.856263377391</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.88</v>
+        <v>-9.44</v>
       </c>
       <c r="L44" t="n">
         <v>10.45</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.59</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H45" t="n">
-        <v>1723.2</v>
+        <v>1785.05</v>
       </c>
       <c r="I45" t="n">
         <v>1773.68316090369</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K45" t="n">
-        <v>2.36</v>
+        <v>-1.15</v>
       </c>
       <c r="L45" t="n">
         <v>2.45</v>
@@ -3006,7 +3545,7 @@
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>3.59</v>
       </c>
       <c r="O45" t="n">
         <v>-1.69</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.35</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="H46" t="n">
-        <v>1948.9</v>
+        <v>1912.8</v>
       </c>
       <c r="I46" t="n">
         <v>1933.492687481676</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K46" t="n">
-        <v>9.18</v>
+        <v>7.16</v>
       </c>
       <c r="L46" t="n">
         <v>4.65</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>7.98</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="H47" t="n">
-        <v>1854.8</v>
+        <v>2020.3</v>
       </c>
       <c r="I47" t="n">
         <v>1949.460475746839</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K47" t="n">
-        <v>3.03</v>
+        <v>-5.62</v>
       </c>
       <c r="L47" t="n">
-        <v>4.45</v>
+        <v>6.65</v>
       </c>
       <c r="M47" t="n">
         <v>4.28</v>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>8.92</v>
       </c>
       <c r="O47" t="n">
         <v>-1.85</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.34</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H48" t="n">
-        <v>1966.2</v>
+        <v>1908.2</v>
       </c>
       <c r="I48" t="n">
         <v>1926.529711134061</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.68</v>
+        <v>-5.55</v>
       </c>
       <c r="L48" t="n">
         <v>6.2</v>
@@ -3177,7 +3752,7 @@
         <v>0.72</v>
       </c>
       <c r="N48" t="n">
-        <v>2.18</v>
+        <v>2.95</v>
       </c>
       <c r="O48" t="n">
         <v>8.92</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.16</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H49" t="n">
-        <v>1909.6</v>
+        <v>1931.7</v>
       </c>
       <c r="I49" t="n">
         <v>1927.745660391774</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.23</v>
       </c>
       <c r="L49" t="n">
         <v>3.28</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.59</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H50" t="n">
-        <v>1855.3</v>
+        <v>1837.1</v>
       </c>
       <c r="I50" t="n">
         <v>1837.442181747823</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.96</v>
+        <v>-4.9</v>
       </c>
       <c r="L50" t="n">
-        <v>4.97</v>
+        <v>5.14</v>
       </c>
       <c r="M50" t="n">
         <v>3.47</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.22</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H51" t="n">
-        <v>1782.2</v>
+        <v>1858</v>
       </c>
       <c r="I51" t="n">
         <v>1815.860459014273</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K51" t="n">
-        <v>2.99</v>
+        <v>-1.14</v>
       </c>
       <c r="L51" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M51" t="n">
         <v>1.61</v>
       </c>
       <c r="N51" t="n">
-        <v>2.32</v>
+        <v>4.25</v>
       </c>
       <c r="O51" t="n">
         <v>-0.98</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H52" t="n">
-        <v>1740.8</v>
+        <v>1732.9</v>
       </c>
       <c r="I52" t="n">
         <v>1733.731158621483</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.31</v>
+        <v>-6.73</v>
       </c>
       <c r="L52" t="n">
         <v>7.51</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.9</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H53" t="n">
-        <v>1790.5</v>
+        <v>1839</v>
       </c>
       <c r="I53" t="n">
         <v>1831.282191599098</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.32</v>
+        <v>-6.12</v>
       </c>
       <c r="L53" t="n">
-        <v>4.01</v>
+        <v>6.41</v>
       </c>
       <c r="M53" t="n">
         <v>1.14</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.82</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="H54" t="n">
-        <v>1814.6</v>
+        <v>1623.8</v>
       </c>
       <c r="I54" t="n">
         <v>1733.423873714384</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.33</v>
+        <v>-11.7</v>
       </c>
       <c r="L54" t="n">
-        <v>5.76</v>
+        <v>16.01</v>
       </c>
       <c r="M54" t="n">
-        <v>1.11</v>
+        <v>6.32</v>
       </c>
       <c r="N54" t="n">
-        <v>2.51</v>
+        <v>10.51</v>
       </c>
       <c r="O54" t="n">
         <v>2.71</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.78</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H55" t="n">
-        <v>1500.6</v>
+        <v>1577</v>
       </c>
       <c r="I55" t="n">
         <v>1530.672672200932</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K55" t="n">
-        <v>7.59</v>
+        <v>2.88</v>
       </c>
       <c r="L55" t="n">
         <v>9.07</v>
@@ -3576,7 +4235,7 @@
         <v>5.14</v>
       </c>
       <c r="N55" t="n">
-        <v>3.5</v>
+        <v>5.09</v>
       </c>
       <c r="O55" t="n">
         <v>-10.51</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3636,6 +4307,14 @@
       <c r="Q56" t="n">
         <v>23</v>
       </c>
+      <c r="R56" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7506,7 +8185,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.1</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="6">
@@ -7516,7 +8195,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -7526,7 +8205,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -7536,7 +8215,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7546,7 +8225,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -7556,7 +8235,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.7</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="11">
@@ -7596,7 +8275,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.96</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="15">
@@ -7606,7 +8285,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.42</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="16">
@@ -7616,7 +8295,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.49</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="17">
@@ -7626,7 +8305,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.7</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="18">
@@ -7636,7 +8315,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -7646,7 +8325,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.91</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="20">
@@ -7656,7 +8335,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.42</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="21">
@@ -7666,7 +8345,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.83</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="22">
@@ -7676,7 +8355,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -7686,7 +8365,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -7696,7 +8375,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="25">
@@ -7716,7 +8395,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.96</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="27">
@@ -7736,7 +8415,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
